--- a/static/data/exports/Retro_UK_GE_2014.xlsx
+++ b/static/data/exports/Retro_UK_GE_2014.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="Q2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>21</v>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="Q3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>21</v>
@@ -1027,11 +1027,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1486865</v>
+        <v>1486864</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Raju Maurya</t>
+          <t>Barhm Dev Jha</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Raju Maurya</t>
+          <t>Barhm Dev Jha</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1089,11 +1089,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1486864</v>
+        <v>1486865</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Barhm Dev Jha</t>
+          <t>Raju Maurya</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Barhm Dev Jha</t>
+          <t>Raju Maurya</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="Q19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>21</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Q20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>21</v>
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="Q36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>21</v>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="Q37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>21</v>
@@ -3321,11 +3321,11 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1487012</v>
+        <v>1487011</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Jai Prakash Upadhyay</t>
+          <t>Gaurav Pundir</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Jai Prakash Upadhyay</t>
+          <t>Gaurav Pundir</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3383,11 +3383,11 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1487011</v>
+        <v>1487012</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Gaurav Pundir</t>
+          <t>Jai Prakash Upadhyay</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Gaurav Pundir</t>
+          <t>Jai Prakash Upadhyay</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="Q54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
         <v>21</v>
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="Q65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>21</v>
@@ -5165,7 +5165,7 @@
         </is>
       </c>
       <c r="Q76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>21</v>
@@ -5847,7 +5847,7 @@
         </is>
       </c>
       <c r="Q87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>21</v>
@@ -6529,7 +6529,7 @@
         </is>
       </c>
       <c r="Q98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
         <v>21</v>
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="Q108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R108" t="n">
         <v>21</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Q109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
         <v>21</v>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="Q126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
         <v>21</v>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="Q137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
         <v>21</v>
@@ -9567,7 +9567,7 @@
         </is>
       </c>
       <c r="Q147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R147" t="n">
         <v>21</v>
@@ -9629,7 +9629,7 @@
         </is>
       </c>
       <c r="Q148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
         <v>21</v>
@@ -10621,7 +10621,7 @@
         </is>
       </c>
       <c r="Q164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R164" t="n">
         <v>21</v>
@@ -10683,7 +10683,7 @@
         </is>
       </c>
       <c r="Q165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R165" t="n">
         <v>21</v>
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="Q181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R181" t="n">
         <v>21</v>
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="Q182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
         <v>21</v>
@@ -12729,7 +12729,7 @@
         </is>
       </c>
       <c r="Q198" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
         <v>21</v>
@@ -12791,7 +12791,7 @@
         </is>
       </c>
       <c r="Q199" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R199" t="n">
         <v>21</v>
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="Q215" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R215" t="n">
         <v>21</v>
@@ -13845,7 +13845,7 @@
         </is>
       </c>
       <c r="Q216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R216" t="n">
         <v>21</v>
@@ -14837,7 +14837,7 @@
         </is>
       </c>
       <c r="Q232" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R232" t="n">
         <v>21</v>
@@ -14899,7 +14899,7 @@
         </is>
       </c>
       <c r="Q233" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R233" t="n">
         <v>21</v>
@@ -15953,7 +15953,7 @@
         </is>
       </c>
       <c r="Q250" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R250" t="n">
         <v>21</v>
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="Q274" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R274" t="n">
         <v>21</v>
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="Q275" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R275" t="n">
         <v>21</v>
@@ -18495,7 +18495,7 @@
         </is>
       </c>
       <c r="Q291" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R291" t="n">
         <v>21</v>
@@ -18557,7 +18557,7 @@
         </is>
       </c>
       <c r="Q292" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R292" t="n">
         <v>21</v>
@@ -19549,7 +19549,7 @@
         </is>
       </c>
       <c r="Q308" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R308" t="n">
         <v>21</v>
@@ -19611,7 +19611,7 @@
         </is>
       </c>
       <c r="Q309" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R309" t="n">
         <v>21</v>
@@ -20123,20 +20123,20 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>1488440</v>
+        <v>1488441</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Navneet Singh Gosain</t>
+          <t>Jai Prakash Upadhyay</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>raup</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>16074</v>
+        <v>16059</v>
       </c>
       <c r="E318" t="n">
         <v>57</v>
@@ -20160,12 +20160,12 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>Navneet Singh Gosain</t>
+          <t>Jai Prakash Upadhyay</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>raup</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q318" t="b">
@@ -20185,20 +20185,20 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>1488441</v>
+        <v>1488440</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Jai Prakash Upadhyay</t>
+          <t>Navneet Singh Gosain</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>raup</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>16059</v>
+        <v>16074</v>
       </c>
       <c r="E319" t="n">
         <v>57</v>
@@ -20222,12 +20222,12 @@
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>Jai Prakash Upadhyay</t>
+          <t>Navneet Singh Gosain</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>raup</t>
         </is>
       </c>
       <c r="Q319" t="b">
@@ -20603,7 +20603,7 @@
         </is>
       </c>
       <c r="Q325" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R325" t="n">
         <v>21</v>
@@ -20665,7 +20665,7 @@
         </is>
       </c>
       <c r="Q326" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R326" t="n">
         <v>21</v>
@@ -21719,7 +21719,7 @@
         </is>
       </c>
       <c r="Q343" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R343" t="n">
         <v>21</v>
@@ -23269,7 +23269,7 @@
         </is>
       </c>
       <c r="Q368" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R368" t="n">
         <v>21</v>
@@ -24819,7 +24819,7 @@
         </is>
       </c>
       <c r="Q393" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R393" t="n">
         <v>21</v>
@@ -25827,20 +25827,20 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>1488843</v>
+        <v>1488842</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Rakesh</t>
+          <t>Sanjay Goyal</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NADP</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>16059</v>
+        <v>16075</v>
       </c>
       <c r="E410" t="n">
         <v>52</v>
@@ -25864,12 +25864,12 @@
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>Rakesh</t>
+          <t>Sanjay Goyal</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NADP</t>
         </is>
       </c>
       <c r="Q410" t="b">
@@ -25889,20 +25889,20 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>1488842</v>
+        <v>1488843</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Sanjay Goyal</t>
+          <t>Rakesh</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>NADP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>16075</v>
+        <v>16059</v>
       </c>
       <c r="E411" t="n">
         <v>52</v>
@@ -25926,12 +25926,12 @@
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>Sanjay Goyal</t>
+          <t>Rakesh</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>NADP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q411" t="b">
@@ -26369,7 +26369,7 @@
         </is>
       </c>
       <c r="Q418" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R418" t="n">
         <v>21</v>
@@ -27857,7 +27857,7 @@
         </is>
       </c>
       <c r="Q442" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R442" t="n">
         <v>21</v>
@@ -28369,11 +28369,11 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>1489047</v>
+        <v>1489046</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Asraf</t>
+          <t>Abdul Aleem</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -28406,7 +28406,7 @@
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t>Asraf</t>
+          <t>Abdul Aleem</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
@@ -28431,11 +28431,11 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>1489046</v>
+        <v>1489047</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Abdul Aleem</t>
+          <t>Asraf</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -28468,7 +28468,7 @@
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>Abdul Aleem</t>
+          <t>Asraf</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
@@ -28803,20 +28803,20 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>1489053</v>
+        <v>1489054</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Sanjay Goyal</t>
+          <t>Sunil</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>NADP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>16075</v>
+        <v>16059</v>
       </c>
       <c r="E458" t="n">
         <v>82</v>
@@ -28840,12 +28840,12 @@
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>Sanjay Goyal</t>
+          <t>Sunil</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
         <is>
-          <t>NADP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q458" t="b">
@@ -28865,20 +28865,20 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>1489054</v>
+        <v>1489053</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Sunil</t>
+          <t>Sanjay Goyal</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NADP</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>16059</v>
+        <v>16075</v>
       </c>
       <c r="E459" t="n">
         <v>82</v>
@@ -28902,12 +28902,12 @@
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t>Sunil</t>
+          <t>Sanjay Goyal</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NADP</t>
         </is>
       </c>
       <c r="Q459" t="b">
@@ -29407,7 +29407,7 @@
         </is>
       </c>
       <c r="Q467" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R467" t="n">
         <v>21</v>
@@ -31019,7 +31019,7 @@
         </is>
       </c>
       <c r="Q493" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R493" t="n">
         <v>21</v>
@@ -32507,7 +32507,7 @@
         </is>
       </c>
       <c r="Q517" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R517" t="n">
         <v>21</v>
@@ -34119,7 +34119,7 @@
         </is>
       </c>
       <c r="Q543" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R543" t="n">
         <v>21</v>
@@ -35065,20 +35065,20 @@
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>1489426</v>
+        <v>1489427</v>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Sanjay Goyal</t>
+          <t>Rakesh</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>NADP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D559" t="n">
-        <v>16075</v>
+        <v>16059</v>
       </c>
       <c r="E559" t="n">
         <v>23</v>
@@ -35102,12 +35102,12 @@
       </c>
       <c r="K559" t="inlineStr">
         <is>
-          <t>Sanjay Goyal</t>
+          <t>Rakesh</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t>NADP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q559" t="b">
@@ -35127,20 +35127,20 @@
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>1489427</v>
+        <v>1489426</v>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Rakesh</t>
+          <t>Sanjay Goyal</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NADP</t>
         </is>
       </c>
       <c r="D560" t="n">
-        <v>16059</v>
+        <v>16075</v>
       </c>
       <c r="E560" t="n">
         <v>23</v>
@@ -35164,12 +35164,12 @@
       </c>
       <c r="K560" t="inlineStr">
         <is>
-          <t>Rakesh</t>
+          <t>Sanjay Goyal</t>
         </is>
       </c>
       <c r="L560" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NADP</t>
         </is>
       </c>
       <c r="Q560" t="b">
@@ -35669,7 +35669,7 @@
         </is>
       </c>
       <c r="Q568" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R568" t="n">
         <v>21</v>
@@ -37157,7 +37157,7 @@
         </is>
       </c>
       <c r="Q592" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R592" t="n">
         <v>21</v>
@@ -38227,20 +38227,20 @@
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>1489621</v>
+        <v>1489622</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Vishal Chaudhary</t>
+          <t>Sanjay Goyal</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>NADP</t>
         </is>
       </c>
       <c r="D610" t="n">
-        <v>16099</v>
+        <v>16075</v>
       </c>
       <c r="E610" t="n">
         <v>48</v>
@@ -38264,12 +38264,12 @@
       </c>
       <c r="K610" t="inlineStr">
         <is>
-          <t>Vishal Chaudhary</t>
+          <t>Sanjay Goyal</t>
         </is>
       </c>
       <c r="L610" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>NADP</t>
         </is>
       </c>
       <c r="Q610" t="b">
@@ -38289,20 +38289,20 @@
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>1489622</v>
+        <v>1489621</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Sanjay Goyal</t>
+          <t>Vishal Chaudhary</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>NADP</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="D611" t="n">
-        <v>16075</v>
+        <v>16099</v>
       </c>
       <c r="E611" t="n">
         <v>48</v>
@@ -38326,12 +38326,12 @@
       </c>
       <c r="K611" t="inlineStr">
         <is>
-          <t>Sanjay Goyal</t>
+          <t>Vishal Chaudhary</t>
         </is>
       </c>
       <c r="L611" t="inlineStr">
         <is>
-          <t>NADP</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="Q611" t="b">
@@ -38769,7 +38769,7 @@
         </is>
       </c>
       <c r="Q618" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R618" t="n">
         <v>21</v>
@@ -39839,20 +39839,20 @@
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>1489715</v>
+        <v>1489716</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Anand Kumar Verma</t>
+          <t>V.K.Kampani</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>HKRD</t>
+          <t>PHRC</t>
         </is>
       </c>
       <c r="D636" t="n">
-        <v>16116</v>
+        <v>16119</v>
       </c>
       <c r="E636" t="n">
         <v>39</v>
@@ -39876,12 +39876,12 @@
       </c>
       <c r="K636" t="inlineStr">
         <is>
-          <t>Anand Kumar Verma</t>
+          <t>V.K.Kampani</t>
         </is>
       </c>
       <c r="L636" t="inlineStr">
         <is>
-          <t>HKRD</t>
+          <t>PHRC</t>
         </is>
       </c>
       <c r="Q636" t="b">
@@ -39901,20 +39901,20 @@
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>1489716</v>
+        <v>1489715</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>V.K.Kampani</t>
+          <t>Anand Kumar Verma</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>PHRC</t>
+          <t>HKRD</t>
         </is>
       </c>
       <c r="D637" t="n">
-        <v>16119</v>
+        <v>16116</v>
       </c>
       <c r="E637" t="n">
         <v>39</v>
@@ -39938,12 +39938,12 @@
       </c>
       <c r="K637" t="inlineStr">
         <is>
-          <t>V.K.Kampani</t>
+          <t>Anand Kumar Verma</t>
         </is>
       </c>
       <c r="L637" t="inlineStr">
         <is>
-          <t>PHRC</t>
+          <t>HKRD</t>
         </is>
       </c>
       <c r="Q637" t="b">
@@ -40319,7 +40319,7 @@
         </is>
       </c>
       <c r="Q643" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R643" t="n">
         <v>21</v>
@@ -41451,20 +41451,20 @@
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>1489817</v>
+        <v>1489816</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Pramod Rana</t>
+          <t>Anand Kumar Verma</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HKRD</t>
         </is>
       </c>
       <c r="D662" t="n">
-        <v>16059</v>
+        <v>16116</v>
       </c>
       <c r="E662" t="n">
         <v>62</v>
@@ -41488,12 +41488,12 @@
       </c>
       <c r="K662" t="inlineStr">
         <is>
-          <t>Pramod Rana</t>
+          <t>Anand Kumar Verma</t>
         </is>
       </c>
       <c r="L662" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HKRD</t>
         </is>
       </c>
       <c r="Q662" t="b">
@@ -41513,20 +41513,20 @@
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>1489816</v>
+        <v>1489817</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Anand Kumar Verma</t>
+          <t>Pramod Rana</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>HKRD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D663" t="n">
-        <v>16116</v>
+        <v>16059</v>
       </c>
       <c r="E663" t="n">
         <v>62</v>
@@ -41550,12 +41550,12 @@
       </c>
       <c r="K663" t="inlineStr">
         <is>
-          <t>Anand Kumar Verma</t>
+          <t>Pramod Rana</t>
         </is>
       </c>
       <c r="L663" t="inlineStr">
         <is>
-          <t>HKRD</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q663" t="b">
@@ -41869,7 +41869,7 @@
         </is>
       </c>
       <c r="Q668" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R668" t="n">
         <v>21</v>
@@ -42551,7 +42551,7 @@
         </is>
       </c>
       <c r="Q679" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R679" t="n">
         <v>21</v>
@@ -43233,7 +43233,7 @@
         </is>
       </c>
       <c r="Q690" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R690" t="n">
         <v>21</v>
@@ -43915,7 +43915,7 @@
         </is>
       </c>
       <c r="Q701" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R701" t="n">
         <v>21</v>
@@ -44597,7 +44597,7 @@
         </is>
       </c>
       <c r="Q712" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R712" t="n">
         <v>21</v>
@@ -45279,7 +45279,7 @@
         </is>
       </c>
       <c r="Q723" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R723" t="n">
         <v>21</v>
@@ -54347,20 +54347,20 @@
     </row>
     <row r="870">
       <c r="A870" t="n">
-        <v>1490926</v>
+        <v>1490927</v>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>Amar Prakash</t>
+          <t>Bhagawati Prasad Trikoti</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>UPP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D870" t="n">
-        <v>16166</v>
+        <v>16079</v>
       </c>
       <c r="E870" t="n">
         <v>116</v>
@@ -54384,12 +54384,12 @@
       </c>
       <c r="K870" t="inlineStr">
         <is>
-          <t>Amar Prakash</t>
+          <t>Bhagawati Prasad Trikoti</t>
         </is>
       </c>
       <c r="L870" t="inlineStr">
         <is>
-          <t>UPP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="Q870" t="b">
@@ -54409,20 +54409,20 @@
     </row>
     <row r="871">
       <c r="A871" t="n">
-        <v>1490927</v>
+        <v>1490926</v>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Bhagawati Prasad Trikoti</t>
+          <t>Amar Prakash</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>UPP</t>
         </is>
       </c>
       <c r="D871" t="n">
-        <v>16079</v>
+        <v>16166</v>
       </c>
       <c r="E871" t="n">
         <v>116</v>
@@ -54446,12 +54446,12 @@
       </c>
       <c r="K871" t="inlineStr">
         <is>
-          <t>Bhagawati Prasad Trikoti</t>
+          <t>Amar Prakash</t>
         </is>
       </c>
       <c r="L871" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>UPP</t>
         </is>
       </c>
       <c r="Q871" t="b">
@@ -59601,7 +59601,7 @@
         </is>
       </c>
       <c r="Q954" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R954" t="n">
         <v>21</v>
@@ -61973,20 +61973,20 @@
     </row>
     <row r="993">
       <c r="A993" t="n">
-        <v>1491483</v>
+        <v>1491482</v>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>Kailash Pandey</t>
+          <t>Asharam Kashyap</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
         <is>
-          <t>CPI(ML)(L)</t>
+          <t>RMGP</t>
         </is>
       </c>
       <c r="D993" t="n">
-        <v>16088</v>
+        <v>16152</v>
       </c>
       <c r="E993" t="n">
         <v>42</v>
@@ -62010,12 +62010,12 @@
       </c>
       <c r="K993" t="inlineStr">
         <is>
-          <t>Kailash Pandey</t>
+          <t>Asharam Kashyap</t>
         </is>
       </c>
       <c r="L993" t="inlineStr">
         <is>
-          <t>CPI(ML)(L)</t>
+          <t>RMGP</t>
         </is>
       </c>
       <c r="Q993" t="b">
@@ -62035,20 +62035,20 @@
     </row>
     <row r="994">
       <c r="A994" t="n">
-        <v>1491482</v>
+        <v>1491483</v>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>Asharam Kashyap</t>
+          <t>Kailash Pandey</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>RMGP</t>
+          <t>CPI(ML)(L)</t>
         </is>
       </c>
       <c r="D994" t="n">
-        <v>16152</v>
+        <v>16088</v>
       </c>
       <c r="E994" t="n">
         <v>42</v>
@@ -62072,12 +62072,12 @@
       </c>
       <c r="K994" t="inlineStr">
         <is>
-          <t>Asharam Kashyap</t>
+          <t>Kailash Pandey</t>
         </is>
       </c>
       <c r="L994" t="inlineStr">
         <is>
-          <t>RMGP</t>
+          <t>CPI(ML)(L)</t>
         </is>
       </c>
       <c r="Q994" t="b">
@@ -66375,20 +66375,20 @@
     </row>
     <row r="1064">
       <c r="A1064" t="n">
-        <v>1491809</v>
+        <v>1491810</v>
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>Avtar Singh</t>
+          <t>None Of The Above</t>
         </is>
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>NOTA</t>
         </is>
       </c>
       <c r="D1064" t="n">
-        <v>16079</v>
+        <v>16061</v>
       </c>
       <c r="E1064" t="n">
         <v>498</v>
@@ -66412,12 +66412,12 @@
       </c>
       <c r="K1064" t="inlineStr">
         <is>
-          <t>Avtar Singh</t>
+          <t>None Of The Above</t>
         </is>
       </c>
       <c r="L1064" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>NOTA</t>
         </is>
       </c>
       <c r="Q1064" t="b">
@@ -66437,20 +66437,20 @@
     </row>
     <row r="1065">
       <c r="A1065" t="n">
-        <v>1491810</v>
+        <v>1491809</v>
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>None Of The Above</t>
+          <t>Avtar Singh</t>
         </is>
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>NOTA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D1065" t="n">
-        <v>16061</v>
+        <v>16079</v>
       </c>
       <c r="E1065" t="n">
         <v>498</v>
@@ -66474,12 +66474,12 @@
       </c>
       <c r="K1065" t="inlineStr">
         <is>
-          <t>None Of The Above</t>
+          <t>Avtar Singh</t>
         </is>
       </c>
       <c r="L1065" t="inlineStr">
         <is>
-          <t>NOTA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="Q1065" t="b">

--- a/static/data/exports/Retro_UK_GE_2014.xlsx
+++ b/static/data/exports/Retro_UK_GE_2014.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1027,11 +1027,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1486864</v>
+        <v>1486865</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Barhm Dev Jha</t>
+          <t>Raju Maurya</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Barhm Dev Jha</t>
+          <t>Raju Maurya</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1089,11 +1089,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1486865</v>
+        <v>1486864</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Raju Maurya</t>
+          <t>Barhm Dev Jha</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Raju Maurya</t>
+          <t>Barhm Dev Jha</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -10203,20 +10203,20 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1487628</v>
+        <v>1487629</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Navneet Singh Gosain</t>
+          <t>Gaurav Pundir</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>raup</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>16074</v>
+        <v>16059</v>
       </c>
       <c r="E158" t="n">
         <v>136</v>
@@ -10240,12 +10240,12 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Navneet Singh Gosain</t>
+          <t>Gaurav Pundir</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>raup</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q158" t="b">
@@ -10265,20 +10265,20 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1487629</v>
+        <v>1487628</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Gaurav Pundir</t>
+          <t>Navneet Singh Gosain</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>raup</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>16059</v>
+        <v>16074</v>
       </c>
       <c r="E159" t="n">
         <v>136</v>
@@ -10302,12 +10302,12 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Gaurav Pundir</t>
+          <t>Navneet Singh Gosain</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>raup</t>
         </is>
       </c>
       <c r="Q159" t="b">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -13241,11 +13241,11 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1487862</v>
+        <v>1487863</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Jai Prakash Upadhyay</t>
+          <t>Raju Maurya</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Jai Prakash Upadhyay</t>
+          <t>Raju Maurya</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -13303,11 +13303,11 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1487863</v>
+        <v>1487862</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Raju Maurya</t>
+          <t>Jai Prakash Upadhyay</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Raju Maurya</t>
+          <t>Jai Prakash Upadhyay</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -14180,7 +14180,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -17714,7 +17714,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D279" t="n">
@@ -18892,7 +18892,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D298" t="n">
@@ -19822,7 +19822,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D313" t="n">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D331" t="n">
@@ -24091,20 +24091,20 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>1488734</v>
+        <v>1488733</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Rakesh</t>
+          <t>Vishal Chaudhary</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>16059</v>
+        <v>16099</v>
       </c>
       <c r="E382" t="n">
         <v>89</v>
@@ -24128,12 +24128,12 @@
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>Rakesh</t>
+          <t>Vishal Chaudhary</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="Q382" t="b">
@@ -24153,20 +24153,20 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>1488733</v>
+        <v>1488734</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Vishal Chaudhary</t>
+          <t>Rakesh</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>16099</v>
+        <v>16059</v>
       </c>
       <c r="E383" t="n">
         <v>89</v>
@@ -24190,12 +24190,12 @@
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>Vishal Chaudhary</t>
+          <t>Rakesh</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q383" t="b">
@@ -24587,20 +24587,20 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>1488742</v>
+        <v>1488741</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Mukesh Saini</t>
+          <t>Pervez Aqil</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>BMUP</t>
+          <t>AIMF</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>16098</v>
+        <v>16120</v>
       </c>
       <c r="E390" t="n">
         <v>52</v>
@@ -24624,12 +24624,12 @@
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>Mukesh Saini</t>
+          <t>Pervez Aqil</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>BMUP</t>
+          <t>AIMF</t>
         </is>
       </c>
       <c r="Q390" t="b">
@@ -24649,20 +24649,20 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>1488741</v>
+        <v>1488742</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Pervez Aqil</t>
+          <t>Mukesh Saini</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>AIMF</t>
+          <t>BMUP</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>16120</v>
+        <v>16098</v>
       </c>
       <c r="E391" t="n">
         <v>52</v>
@@ -24686,12 +24686,12 @@
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>Pervez Aqil</t>
+          <t>Mukesh Saini</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>AIMF</t>
+          <t>BMUP</t>
         </is>
       </c>
       <c r="Q391" t="b">
@@ -28369,11 +28369,11 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>1489046</v>
+        <v>1489047</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Abdul Aleem</t>
+          <t>Asraf</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -28406,7 +28406,7 @@
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t>Abdul Aleem</t>
+          <t>Asraf</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
@@ -28431,11 +28431,11 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>1489047</v>
+        <v>1489046</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Asraf</t>
+          <t>Abdul Aleem</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -28468,7 +28468,7 @@
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>Asraf</t>
+          <t>Abdul Aleem</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
@@ -34817,20 +34817,20 @@
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>1489422</v>
+        <v>1489423</v>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Javed</t>
+          <t>Mohar Singh Kataria</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>ABML(S)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D555" t="n">
-        <v>16118</v>
+        <v>16059</v>
       </c>
       <c r="E555" t="n">
         <v>31</v>
@@ -34854,12 +34854,12 @@
       </c>
       <c r="K555" t="inlineStr">
         <is>
-          <t>Javed</t>
+          <t>Mohar Singh Kataria</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
         <is>
-          <t>ABML(S)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q555" t="b">
@@ -34879,20 +34879,20 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>1489423</v>
+        <v>1489422</v>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Mohar Singh Kataria</t>
+          <t>Javed</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ABML(S)</t>
         </is>
       </c>
       <c r="D556" t="n">
-        <v>16059</v>
+        <v>16118</v>
       </c>
       <c r="E556" t="n">
         <v>31</v>
@@ -34916,12 +34916,12 @@
       </c>
       <c r="K556" t="inlineStr">
         <is>
-          <t>Mohar Singh Kataria</t>
+          <t>Javed</t>
         </is>
       </c>
       <c r="L556" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ABML(S)</t>
         </is>
       </c>
       <c r="Q556" t="b">
@@ -41079,20 +41079,20 @@
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>1489810</v>
+        <v>1489811</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Ramnaresh Yadav</t>
+          <t>Mohar Singh Kataria</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>kajp</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D656" t="n">
-        <v>16117</v>
+        <v>16059</v>
       </c>
       <c r="E656" t="n">
         <v>112</v>
@@ -41116,12 +41116,12 @@
       </c>
       <c r="K656" t="inlineStr">
         <is>
-          <t>Ramnaresh Yadav</t>
+          <t>Mohar Singh Kataria</t>
         </is>
       </c>
       <c r="L656" t="inlineStr">
         <is>
-          <t>kajp</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q656" t="b">
@@ -41141,20 +41141,20 @@
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>1489811</v>
+        <v>1489810</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Mohar Singh Kataria</t>
+          <t>Ramnaresh Yadav</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>kajp</t>
         </is>
       </c>
       <c r="D657" t="n">
-        <v>16059</v>
+        <v>16117</v>
       </c>
       <c r="E657" t="n">
         <v>112</v>
@@ -41178,12 +41178,12 @@
       </c>
       <c r="K657" t="inlineStr">
         <is>
-          <t>Mohar Singh Kataria</t>
+          <t>Ramnaresh Yadav</t>
         </is>
       </c>
       <c r="L657" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>kajp</t>
         </is>
       </c>
       <c r="Q657" t="b">
@@ -54347,20 +54347,20 @@
     </row>
     <row r="870">
       <c r="A870" t="n">
-        <v>1490927</v>
+        <v>1490928</v>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>Bhagawati Prasad Trikoti</t>
+          <t>Vijay Kumar</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>CPI(ML)(L)</t>
         </is>
       </c>
       <c r="D870" t="n">
-        <v>16079</v>
+        <v>16088</v>
       </c>
       <c r="E870" t="n">
         <v>116</v>
@@ -54384,12 +54384,12 @@
       </c>
       <c r="K870" t="inlineStr">
         <is>
-          <t>Bhagawati Prasad Trikoti</t>
+          <t>Vijay Kumar</t>
         </is>
       </c>
       <c r="L870" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>CPI(ML)(L)</t>
         </is>
       </c>
       <c r="Q870" t="b">
@@ -54409,20 +54409,20 @@
     </row>
     <row r="871">
       <c r="A871" t="n">
-        <v>1490926</v>
+        <v>1490927</v>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Amar Prakash</t>
+          <t>Bhagawati Prasad Trikoti</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>UPP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D871" t="n">
-        <v>16166</v>
+        <v>16079</v>
       </c>
       <c r="E871" t="n">
         <v>116</v>
@@ -54446,12 +54446,12 @@
       </c>
       <c r="K871" t="inlineStr">
         <is>
-          <t>Amar Prakash</t>
+          <t>Bhagawati Prasad Trikoti</t>
         </is>
       </c>
       <c r="L871" t="inlineStr">
         <is>
-          <t>UPP</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="Q871" t="b">
@@ -54471,20 +54471,20 @@
     </row>
     <row r="872">
       <c r="A872" t="n">
-        <v>1490928</v>
+        <v>1490926</v>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>Vijay Kumar</t>
+          <t>Amar Prakash</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>CPI(ML)(L)</t>
+          <t>UPP</t>
         </is>
       </c>
       <c r="D872" t="n">
-        <v>16088</v>
+        <v>16166</v>
       </c>
       <c r="E872" t="n">
         <v>116</v>
@@ -54508,12 +54508,12 @@
       </c>
       <c r="K872" t="inlineStr">
         <is>
-          <t>Vijay Kumar</t>
+          <t>Amar Prakash</t>
         </is>
       </c>
       <c r="L872" t="inlineStr">
         <is>
-          <t>CPI(ML)(L)</t>
+          <t>UPP</t>
         </is>
       </c>
       <c r="Q872" t="b">
